--- a/financials/MWG/MWG_Q.xlsx
+++ b/financials/MWG/MWG_Q.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28935" yWindow="-135" windowWidth="29070" windowHeight="15870" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="4545" windowWidth="24000" windowHeight="8355" tabRatio="600" firstSheet="1" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,9 +12,6 @@
     <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Dự báo tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +30,7 @@
   </numFmts>
   <fonts count="15">
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -64,7 +61,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -226,7 +223,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -285,16 +282,10 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
@@ -327,6 +318,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -369,20 +374,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -471,25 +462,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="G2">
-            <v>75100</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11362,14 +11334,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J85"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="12.75"/>
   <cols>
-    <col width="40.6640625" customWidth="1" style="5" min="1" max="1"/>
-    <col width="18.88671875" customWidth="1" style="5" min="2" max="8"/>
-    <col width="21.88671875" bestFit="1" customWidth="1" style="5" min="9" max="9"/>
-    <col width="20.5546875" bestFit="1" customWidth="1" style="5" min="10" max="10"/>
+    <col width="40.625" customWidth="1" style="5" min="1" max="1"/>
+    <col width="18.875" customWidth="1" style="5" min="2" max="8"/>
+    <col width="21.875" bestFit="1" customWidth="1" style="5" min="9" max="9"/>
+    <col width="20.5" bestFit="1" customWidth="1" style="5" min="10" max="10"/>
     <col width="9" customWidth="1" style="5" min="11" max="11"/>
-    <col width="8.88671875" customWidth="1" style="5" min="12" max="16384"/>
+    <col width="8.875" customWidth="1" style="5" min="12" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11425,35 +11397,35 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="19">
         <f>IFERROR(C$51/((C$39+B$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D2" s="46">
+      <c r="D2" s="19">
         <f>IFERROR(D$51/((D$39+C$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E2" s="46">
+      <c r="E2" s="19">
         <f>IFERROR(E$51/((E$39+D$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="19">
         <f>IFERROR(F$51/((F$39+E$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G2" s="46">
+      <c r="G2" s="19">
         <f>IFERROR(G$51/((G$39+F$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H2" s="46">
+      <c r="H2" s="19">
         <f>IFERROR(H$51/((H$39+G$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I2" s="46">
+      <c r="I2" s="19">
         <f>IFERROR(I$51/((I$39+H$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="J2" s="46">
+      <c r="J2" s="19">
         <f>IFERROR(J$51/((J$39+I$39)/2),"n/a")</f>
         <v/>
       </c>
@@ -11469,31 +11441,31 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="C3" s="46">
+      <c r="C3" s="19">
         <f>IFERROR(C$50/((C$31+B$31)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D3" s="46">
+      <c r="D3" s="19">
         <f>IFERROR(D$50/((D$31+C$31)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="19">
         <f>IFERROR(E$50/((E$31+D$31)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="19">
         <f>IFERROR(F$50/((F$31+E$31)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G3" s="46">
+      <c r="G3" s="19">
         <f>IFERROR(G$50/((G$31+F$31)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H3" s="46">
+      <c r="H3" s="19">
         <f>IFERROR(H$50/((H$31+G$31)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I3" s="46">
+      <c r="I3" s="19">
         <f>IFERROR(I$50/((I$31+H$31)/2),"n/a")</f>
         <v/>
       </c>
@@ -11509,35 +11481,35 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="19">
         <f>IFERROR((C$51-B$51)/ABS(B$51),"n/a")</f>
         <v/>
       </c>
-      <c r="D4" s="46">
+      <c r="D4" s="19">
         <f>IFERROR((D$51-C$51)/ABS(C$51),"n/a")</f>
         <v/>
       </c>
-      <c r="E4" s="46">
+      <c r="E4" s="19">
         <f>IFERROR((E$51-D$51)/ABS(D$51),"n/a")</f>
         <v/>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="19">
         <f>IFERROR((F$51-E$51)/ABS(E$51),"n/a")</f>
         <v/>
       </c>
-      <c r="G4" s="46">
+      <c r="G4" s="19">
         <f>IFERROR((G$51-F$51)/ABS(F$51),"n/a")</f>
         <v/>
       </c>
-      <c r="H4" s="46">
+      <c r="H4" s="19">
         <f>IFERROR((H$51-G$51)/ABS(G$51),"n/a")</f>
         <v/>
       </c>
-      <c r="I4" s="46">
+      <c r="I4" s="19">
         <f>IFERROR((I$51-H$51)/ABS(H$51),"n/a")</f>
         <v/>
       </c>
-      <c r="J4" s="46">
+      <c r="J4" s="19">
         <f>IFERROR((J$51-I$51)/ABS(I$51),"n/a")</f>
         <v/>
       </c>
@@ -11553,35 +11525,35 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="19">
         <f>IFERROR((C$43-B$43)/ABS(B$43),"n/a")</f>
         <v/>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="19">
         <f>IFERROR((D$43-C$43)/ABS(C$43),"n/a")</f>
         <v/>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="19">
         <f>IFERROR((E$43-D$43)/ABS(D$43),"n/a")</f>
         <v/>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="19">
         <f>IFERROR((F$43-E$43)/ABS(E$43),"n/a")</f>
         <v/>
       </c>
-      <c r="G5" s="46">
+      <c r="G5" s="19">
         <f>IFERROR((G$43-F$43)/ABS(F$43),"n/a")</f>
         <v/>
       </c>
-      <c r="H5" s="46">
+      <c r="H5" s="19">
         <f>IFERROR((H$43-G$43)/ABS(G$43),"n/a")</f>
         <v/>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="19">
         <f>IFERROR((I$43-H$43)/ABS(H$43),"n/a")</f>
         <v/>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="19">
         <f>IFERROR((J$43-I$43)/ABS(I$43),"n/a")</f>
         <v/>
       </c>
@@ -11592,35 +11564,35 @@
           <t>Biên lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B6" s="46">
+      <c r="B6" s="19">
         <f>IFERROR(B$45/B$43,"n/a")</f>
         <v/>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="19">
         <f>IFERROR(C$45/C$43,"n/a")</f>
         <v/>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="19">
         <f>IFERROR(D$45/D$43,"n/a")</f>
         <v/>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="19">
         <f>IFERROR(E$45/E$43,"n/a")</f>
         <v/>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="19">
         <f>IFERROR(F$45/F$43,"n/a")</f>
         <v/>
       </c>
-      <c r="G6" s="46">
+      <c r="G6" s="19">
         <f>IFERROR(G$45/G$43,"n/a")</f>
         <v/>
       </c>
-      <c r="H6" s="46">
+      <c r="H6" s="19">
         <f>IFERROR(H$45/H$43,"n/a")</f>
         <v/>
       </c>
-      <c r="I6" s="46">
+      <c r="I6" s="19">
         <f>IFERROR(I$45/I$43,"n/a")</f>
         <v/>
       </c>
@@ -11631,39 +11603,39 @@
           <t>Biên lợi nhuận ròng</t>
         </is>
       </c>
-      <c r="B7" s="46">
+      <c r="B7" s="19">
         <f>IFERROR(B$51/B$43,"n/a")</f>
         <v/>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="19">
         <f>IFERROR(C$51/C$43,"n/a")</f>
         <v/>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="19">
         <f>IFERROR(D$51/D$43,"n/a")</f>
         <v/>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="19">
         <f>IFERROR(E$51/E$43,"n/a")</f>
         <v/>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="19">
         <f>IFERROR(F$51/F$43,"n/a")</f>
         <v/>
       </c>
-      <c r="G7" s="46">
+      <c r="G7" s="19">
         <f>IFERROR(G$51/G$43,"n/a")</f>
         <v/>
       </c>
-      <c r="H7" s="46">
+      <c r="H7" s="19">
         <f>IFERROR(H$51/H$43,"n/a")</f>
         <v/>
       </c>
-      <c r="I7" s="46">
+      <c r="I7" s="19">
         <f>IFERROR(I$51/I$43,"n/a")</f>
         <v/>
       </c>
-      <c r="J7" s="46">
+      <c r="J7" s="19">
         <f>IFERROR(J$51/J$43,"n/a")</f>
         <v/>
       </c>
@@ -11908,35 +11880,35 @@
           <t>Chi phí bán hàng, quản lý/LN gộp</t>
         </is>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="19">
         <f>IFERROR((ABS(B$46)+ABS(B$47))/B$45,"n/a")</f>
         <v/>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="19">
         <f>IFERROR((ABS(C$46)+ABS(C$47))/C$45,"n/a")</f>
         <v/>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="19">
         <f>IFERROR((ABS(D$46)+ABS(D$47))/D$45,"n/a")</f>
         <v/>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="19">
         <f>IFERROR((ABS(E$46)+ABS(E$47))/E$45,"n/a")</f>
         <v/>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="19">
         <f>IFERROR((ABS(F$46)+ABS(F$47))/F$45,"n/a")</f>
         <v/>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="19">
         <f>IFERROR((ABS(G$46)+ABS(G$47))/G$45,"n/a")</f>
         <v/>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="19">
         <f>IFERROR((ABS(H$46)+ABS(H$47))/H$45,"n/a")</f>
         <v/>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="19">
         <f>IFERROR((ABS(I$46)+ABS(I$47))/I$45,"n/a")</f>
         <v/>
       </c>
@@ -11947,35 +11919,35 @@
           <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="19">
         <f>IFERROR(ABS(B$49)/B$48,"n/a")</f>
         <v/>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="19">
         <f>IFERROR(ABS(C$49)/C$48,"n/a")</f>
         <v/>
       </c>
-      <c r="D15" s="46">
+      <c r="D15" s="19">
         <f>IFERROR(ABS(D$49)/D$48,"n/a")</f>
         <v/>
       </c>
-      <c r="E15" s="46">
+      <c r="E15" s="19">
         <f>IFERROR(ABS(E$49)/E$48,"n/a")</f>
         <v/>
       </c>
-      <c r="F15" s="46">
+      <c r="F15" s="19">
         <f>IFERROR(ABS(F$49)/F$48,"n/a")</f>
         <v/>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="19">
         <f>IFERROR(ABS(G$49)/G$48,"n/a")</f>
         <v/>
       </c>
-      <c r="H15" s="46">
+      <c r="H15" s="19">
         <f>IFERROR(ABS(H$49)/H$48,"n/a")</f>
         <v/>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="19">
         <f>IFERROR(ABS(I$49)/I$48,"n/a")</f>
         <v/>
       </c>
@@ -12106,35 +12078,35 @@
           <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
-      <c r="B19" s="46">
+      <c r="B19" s="19">
         <f>IFERROR(B$26/B$31,"n/a")</f>
         <v/>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="19">
         <f>IFERROR(C$26/C$31,"n/a")</f>
         <v/>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="19">
         <f>IFERROR(D$26/D$31,"n/a")</f>
         <v/>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="19">
         <f>IFERROR(E$26/E$31,"n/a")</f>
         <v/>
       </c>
-      <c r="F19" s="46">
+      <c r="F19" s="19">
         <f>IFERROR(F$26/F$31,"n/a")</f>
         <v/>
       </c>
-      <c r="G19" s="46">
+      <c r="G19" s="19">
         <f>IFERROR(G$26/G$31,"n/a")</f>
         <v/>
       </c>
-      <c r="H19" s="46">
+      <c r="H19" s="19">
         <f>IFERROR(H$26/H$31,"n/a")</f>
         <v/>
       </c>
-      <c r="I19" s="46">
+      <c r="I19" s="19">
         <f>IFERROR(I$26/I$31,"n/a")</f>
         <v/>
       </c>
@@ -12145,35 +12117,35 @@
           <t>Hàng tồn kho/Tài sản</t>
         </is>
       </c>
-      <c r="B20" s="46">
+      <c r="B20" s="19">
         <f>IFERROR(B$28/B$31,"n/a")</f>
         <v/>
       </c>
-      <c r="C20" s="46">
+      <c r="C20" s="19">
         <f>IFERROR(C$28/C$31,"n/a")</f>
         <v/>
       </c>
-      <c r="D20" s="46">
+      <c r="D20" s="19">
         <f>IFERROR(D$28/D$31,"n/a")</f>
         <v/>
       </c>
-      <c r="E20" s="46">
+      <c r="E20" s="19">
         <f>IFERROR(E$28/E$31,"n/a")</f>
         <v/>
       </c>
-      <c r="F20" s="46">
+      <c r="F20" s="19">
         <f>IFERROR(F$28/F$31,"n/a")</f>
         <v/>
       </c>
-      <c r="G20" s="46">
+      <c r="G20" s="19">
         <f>IFERROR(G$28/G$31,"n/a")</f>
         <v/>
       </c>
-      <c r="H20" s="46">
+      <c r="H20" s="19">
         <f>IFERROR(H$28/H$31,"n/a")</f>
         <v/>
       </c>
-      <c r="I20" s="46">
+      <c r="I20" s="19">
         <f>IFERROR(I$28/I$31,"n/a")</f>
         <v/>
       </c>
@@ -12268,35 +12240,35 @@
           <t>Tiền và tương đương tiền</t>
         </is>
       </c>
-      <c r="B26" s="47">
+      <c r="B26" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D26" s="47">
+      <c r="D26" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E26" s="47">
+      <c r="E26" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F26" s="47">
+      <c r="F26" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G26" s="47">
+      <c r="G26" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H26" s="47">
+      <c r="H26" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="47">
+      <c r="I26" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12307,35 +12279,35 @@
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B27" s="47">
+      <c r="B27" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D27" s="47">
+      <c r="D27" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E27" s="47">
+      <c r="E27" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F27" s="47">
+      <c r="F27" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G27" s="47">
+      <c r="G27" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H27" s="47">
+      <c r="H27" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="47">
+      <c r="I27" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12346,35 +12318,35 @@
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B28" s="47">
+      <c r="B28" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D28" s="47">
+      <c r="D28" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E28" s="47">
+      <c r="E28" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F28" s="47">
+      <c r="F28" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G28" s="47">
+      <c r="G28" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H28" s="47">
+      <c r="H28" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="47">
+      <c r="I28" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12385,35 +12357,35 @@
           <t>TÀI SẢN NGẮN HẠN</t>
         </is>
       </c>
-      <c r="B29" s="47">
+      <c r="B29" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D29" s="47">
+      <c r="D29" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E29" s="47">
+      <c r="E29" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F29" s="47">
+      <c r="F29" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G29" s="47">
+      <c r="G29" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H29" s="47">
+      <c r="H29" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="47">
+      <c r="I29" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12424,35 +12396,35 @@
           <t>GTCL tài sản cố định vô hình</t>
         </is>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D30" s="47">
+      <c r="D30" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E30" s="47">
+      <c r="E30" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F30" s="47">
+      <c r="F30" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G30" s="47">
+      <c r="G30" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H30" s="47">
+      <c r="H30" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="47">
+      <c r="I30" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12463,35 +12435,35 @@
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B31" s="47">
+      <c r="B31" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D31" s="47">
+      <c r="D31" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E31" s="47">
+      <c r="E31" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F31" s="47">
+      <c r="F31" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G31" s="47">
+      <c r="G31" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H31" s="47">
+      <c r="H31" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="47">
+      <c r="I31" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12502,14 +12474,14 @@
           <t>Nguồn vốn</t>
         </is>
       </c>
-      <c r="B32" s="47" t="n"/>
-      <c r="C32" s="47" t="n"/>
-      <c r="D32" s="47" t="n"/>
-      <c r="E32" s="47" t="n"/>
-      <c r="F32" s="47" t="n"/>
-      <c r="G32" s="47" t="n"/>
-      <c r="H32" s="47" t="n"/>
-      <c r="I32" s="47" t="n"/>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="28" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="28" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="28" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="27" t="inlineStr">
@@ -12517,35 +12489,35 @@
           <t>Phải trả người bán</t>
         </is>
       </c>
-      <c r="B33" s="47">
+      <c r="B33" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="47">
+      <c r="D33" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="47">
+      <c r="E33" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="47">
+      <c r="F33" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="47">
+      <c r="G33" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="47">
+      <c r="H33" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="47">
+      <c r="I33" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12556,35 +12528,35 @@
           <t>Vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B34" s="47">
+      <c r="B34" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="47">
+      <c r="D34" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="47">
+      <c r="E34" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="47">
+      <c r="F34" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="47">
+      <c r="G34" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="47">
+      <c r="H34" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="47">
+      <c r="I34" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12595,35 +12567,35 @@
           <t>Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B35" s="47">
+      <c r="B35" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="47">
+      <c r="C35" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="47">
+      <c r="D35" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="47">
+      <c r="E35" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="47">
+      <c r="F35" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="47">
+      <c r="G35" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="47">
+      <c r="H35" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="47">
+      <c r="I35" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12634,35 +12606,35 @@
           <t>Vay dài hạn</t>
         </is>
       </c>
-      <c r="B36" s="47">
+      <c r="B36" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="47">
+      <c r="C36" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="47">
+      <c r="D36" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="47">
+      <c r="E36" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="47">
+      <c r="F36" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="47">
+      <c r="G36" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="47">
+      <c r="H36" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="47">
+      <c r="I36" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12673,35 +12645,35 @@
           <t>Nợ dài hạn</t>
         </is>
       </c>
-      <c r="B37" s="47">
+      <c r="B37" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="47">
+      <c r="C37" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="47">
+      <c r="D37" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E37" s="47">
+      <c r="E37" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="47">
+      <c r="F37" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="47">
+      <c r="G37" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="47">
+      <c r="H37" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="47">
+      <c r="I37" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12712,35 +12684,35 @@
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B38" s="47">
+      <c r="B38" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="47">
+      <c r="C38" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D38" s="47">
+      <c r="D38" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E38" s="47">
+      <c r="E38" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="47">
+      <c r="F38" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="47">
+      <c r="G38" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="47">
+      <c r="H38" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="47">
+      <c r="I38" s="28">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12751,39 +12723,39 @@
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B39" s="48">
+      <c r="B39" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="48">
+      <c r="C39" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="48">
+      <c r="D39" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="48">
+      <c r="E39" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="48">
+      <c r="F39" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="48">
+      <c r="G39" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="48">
+      <c r="H39" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="48">
+      <c r="I39" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="J39" s="49">
+      <c r="J39" s="30">
         <f>I39+0.8*J51</f>
         <v/>
       </c>
@@ -12794,7 +12766,7 @@
           <t>Tăng VCSH/LN cổ đông cty mẹ</t>
         </is>
       </c>
-      <c r="B40" s="50" t="n"/>
+      <c r="B40" s="38" t="n"/>
       <c r="C40" s="39">
         <f>(C39-B39)/C51</f>
         <v/>
@@ -12823,7 +12795,7 @@
         <f>(I39-H39)/I51</f>
         <v/>
       </c>
-      <c r="J40" s="51" t="n"/>
+      <c r="J40" s="40" t="n"/>
     </row>
     <row r="41" customFormat="1" s="36">
       <c r="A41" s="15" t="inlineStr">
@@ -12831,35 +12803,35 @@
           <t>Lợi ích cổ đông không kiểm soát</t>
         </is>
       </c>
-      <c r="B41" s="48">
+      <c r="B41" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="48">
+      <c r="C41" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D41" s="48">
+      <c r="D41" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E41" s="48">
+      <c r="E41" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F41" s="48">
+      <c r="F41" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="48">
+      <c r="G41" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="48">
+      <c r="H41" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="48">
+      <c r="I41" s="29">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích cổ đông không kiểm soát",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12885,39 +12857,39 @@
           <t>Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B43" s="48">
+      <c r="B43" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="48">
+      <c r="C43" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="48">
+      <c r="D43" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E43" s="48">
+      <c r="E43" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F43" s="48">
+      <c r="F43" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="48">
+      <c r="G43" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="48">
+      <c r="H43" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I43" s="48">
+      <c r="I43" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="J43" s="48" t="n">
+      <c r="J43" s="29" t="n">
         <v>185000000000000</v>
       </c>
     </row>
@@ -12927,35 +12899,35 @@
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B44" s="47">
+      <c r="B44" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D44" s="47">
+      <c r="D44" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E44" s="47">
+      <c r="E44" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F44" s="47">
+      <c r="F44" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="47">
+      <c r="G44" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="47">
+      <c r="H44" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I44" s="47">
+      <c r="I44" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -12966,35 +12938,35 @@
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B45" s="48">
+      <c r="B45" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C45" s="48">
+      <c r="C45" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D45" s="48">
+      <c r="D45" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E45" s="48">
+      <c r="E45" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F45" s="48">
+      <c r="F45" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G45" s="48">
+      <c r="G45" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H45" s="48">
+      <c r="H45" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I45" s="48">
+      <c r="I45" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -13005,35 +12977,35 @@
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B46" s="47">
+      <c r="B46" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="47">
+      <c r="D46" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="47">
+      <c r="E46" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="47">
+      <c r="F46" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="47">
+      <c r="G46" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="47">
+      <c r="H46" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I46" s="47">
+      <c r="I46" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -13044,35 +13016,35 @@
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B47" s="47">
+      <c r="B47" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="47">
+      <c r="C47" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="47">
+      <c r="D47" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="47">
+      <c r="E47" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="47">
+      <c r="F47" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="47">
+      <c r="G47" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="47">
+      <c r="H47" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I47" s="47">
+      <c r="I47" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -13083,35 +13055,35 @@
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B48" s="47">
+      <c r="B48" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="47">
+      <c r="C48" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="47">
+      <c r="D48" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="47">
+      <c r="E48" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F48" s="47">
+      <c r="F48" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G48" s="47">
+      <c r="G48" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H48" s="47">
+      <c r="H48" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I48" s="47">
+      <c r="I48" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -13122,35 +13094,35 @@
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B49" s="47">
+      <c r="B49" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D49" s="47">
+      <c r="D49" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E49" s="47">
+      <c r="E49" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F49" s="47">
+      <c r="F49" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G49" s="47">
+      <c r="G49" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="47">
+      <c r="I49" s="28">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -13161,39 +13133,39 @@
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B50" s="48">
+      <c r="B50" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C50" s="48">
+      <c r="C50" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D50" s="48">
+      <c r="D50" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E50" s="48">
+      <c r="E50" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F50" s="48">
+      <c r="F50" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G50" s="48">
+      <c r="G50" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H50" s="48">
+      <c r="H50" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I50" s="48">
+      <c r="I50" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="J50" s="48" t="n">
+      <c r="J50" s="29" t="n">
         <v>9200000000000</v>
       </c>
     </row>
@@ -13203,39 +13175,39 @@
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B51" s="48">
+      <c r="B51" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C51" s="48">
+      <c r="C51" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="48">
+      <c r="D51" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E51" s="48">
+      <c r="E51" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F51" s="48">
+      <c r="F51" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G51" s="48">
+      <c r="G51" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H51" s="48">
+      <c r="H51" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I51" s="48">
+      <c r="I51" s="29">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="J51" s="48" t="n">
+      <c r="J51" s="29" t="n">
         <v>9200000000000</v>
       </c>
     </row>
@@ -13260,35 +13232,35 @@
           <t>Khấu hao TSCĐ và BĐSĐT</t>
         </is>
       </c>
-      <c r="B53" s="47">
+      <c r="B53" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C53" s="47">
+      <c r="C53" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D53" s="47">
+      <c r="D53" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E53" s="47">
+      <c r="E53" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F53" s="47">
+      <c r="F53" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G53" s="47">
+      <c r="G53" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H53" s="47">
+      <c r="H53" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I53" s="47">
+      <c r="I53" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -13299,35 +13271,35 @@
           <t>Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B54" s="47">
+      <c r="B54" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C54" s="47">
+      <c r="C54" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D54" s="47">
+      <c r="D54" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E54" s="47">
+      <c r="E54" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F54" s="47">
+      <c r="F54" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G54" s="47">
+      <c r="G54" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H54" s="47">
+      <c r="H54" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I54" s="47">
+      <c r="I54" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -13338,35 +13310,35 @@
           <t>Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
-      <c r="B55" s="47">
+      <c r="B55" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C55" s="47">
+      <c r="C55" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D55" s="47">
+      <c r="D55" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E55" s="47">
+      <c r="E55" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F55" s="47">
+      <c r="F55" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G55" s="47">
+      <c r="G55" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H55" s="47">
+      <c r="H55" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I55" s="47">
+      <c r="I55" s="28">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -13423,35 +13395,35 @@
           <t>ROCE</t>
         </is>
       </c>
-      <c r="B61" s="52">
+      <c r="B61" s="32">
         <f>IFERROR(B$63/(B$31-B$35),"n/a")</f>
         <v/>
       </c>
-      <c r="C61" s="52">
+      <c r="C61" s="32">
         <f>IFERROR(C$63/(C$31-C$35),"n/a")</f>
         <v/>
       </c>
-      <c r="D61" s="52">
+      <c r="D61" s="32">
         <f>IFERROR(D$63/(D$31-D$35),"n/a")</f>
         <v/>
       </c>
-      <c r="E61" s="52">
+      <c r="E61" s="32">
         <f>IFERROR(E$63/(E$31-E$35),"n/a")</f>
         <v/>
       </c>
-      <c r="F61" s="52">
+      <c r="F61" s="32">
         <f>IFERROR(F$63/(F$31-F$35),"n/a")</f>
         <v/>
       </c>
-      <c r="G61" s="52">
+      <c r="G61" s="32">
         <f>IFERROR(G$63/(G$31-G$35),"n/a")</f>
         <v/>
       </c>
-      <c r="H61" s="52">
+      <c r="H61" s="32">
         <f>IFERROR(H$63/(H$31-H$35),"n/a")</f>
         <v/>
       </c>
-      <c r="I61" s="52">
+      <c r="I61" s="32">
         <f>IFERROR(I$63/(I$31-I$35),"n/a")</f>
         <v/>
       </c>
@@ -13462,35 +13434,35 @@
           <t>CROIC</t>
         </is>
       </c>
-      <c r="B62" s="52">
+      <c r="B62" s="32">
         <f>IFERROR(B$67/(B$31-B$35),"n/a")</f>
         <v/>
       </c>
-      <c r="C62" s="52">
+      <c r="C62" s="32">
         <f>IFERROR(C$67/(C$31-C$35),"n/a")</f>
         <v/>
       </c>
-      <c r="D62" s="52">
+      <c r="D62" s="32">
         <f>IFERROR(D$67/(D$31-D$35),"n/a")</f>
         <v/>
       </c>
-      <c r="E62" s="52">
+      <c r="E62" s="32">
         <f>IFERROR(E$67/(E$31-E$35),"n/a")</f>
         <v/>
       </c>
-      <c r="F62" s="52">
+      <c r="F62" s="32">
         <f>IFERROR(F$67/(F$31-F$35),"n/a")</f>
         <v/>
       </c>
-      <c r="G62" s="52">
+      <c r="G62" s="32">
         <f>IFERROR(G$67/(G$31-G$35),"n/a")</f>
         <v/>
       </c>
-      <c r="H62" s="52">
+      <c r="H62" s="32">
         <f>IFERROR(H$67/(H$31-H$35),"n/a")</f>
         <v/>
       </c>
-      <c r="I62" s="52">
+      <c r="I62" s="32">
         <f>IFERROR(I$67/(I$31-I$35),"n/a")</f>
         <v/>
       </c>
@@ -13501,35 +13473,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B63" s="53">
+      <c r="B63" s="33">
         <f>IFERROR(B$48+ABS(B$49),"n/a")</f>
         <v/>
       </c>
-      <c r="C63" s="53">
+      <c r="C63" s="33">
         <f>IFERROR(C$48+ABS(C$49),"n/a")</f>
         <v/>
       </c>
-      <c r="D63" s="53">
+      <c r="D63" s="33">
         <f>IFERROR(D$48+ABS(D$49),"n/a")</f>
         <v/>
       </c>
-      <c r="E63" s="53">
+      <c r="E63" s="33">
         <f>IFERROR(E$48+ABS(E$49),"n/a")</f>
         <v/>
       </c>
-      <c r="F63" s="53">
+      <c r="F63" s="33">
         <f>IFERROR(F$48+ABS(F$49),"n/a")</f>
         <v/>
       </c>
-      <c r="G63" s="53">
+      <c r="G63" s="33">
         <f>IFERROR(G$48+ABS(G$49),"n/a")</f>
         <v/>
       </c>
-      <c r="H63" s="53">
+      <c r="H63" s="33">
         <f>IFERROR(H$48+ABS(H$49),"n/a")</f>
         <v/>
       </c>
-      <c r="I63" s="53">
+      <c r="I63" s="33">
         <f>IFERROR(I$48+ABS(I$49),"n/a")</f>
         <v/>
       </c>
@@ -13540,35 +13512,35 @@
           <t>EBIT/DT</t>
         </is>
       </c>
-      <c r="B64" s="52">
+      <c r="B64" s="32">
         <f>IFERROR(B$63/B$43,"n/a")</f>
         <v/>
       </c>
-      <c r="C64" s="52">
+      <c r="C64" s="32">
         <f>IFERROR(C$63/C$43,"n/a")</f>
         <v/>
       </c>
-      <c r="D64" s="52">
+      <c r="D64" s="32">
         <f>IFERROR(D$63/D$43,"n/a")</f>
         <v/>
       </c>
-      <c r="E64" s="52">
+      <c r="E64" s="32">
         <f>IFERROR(E$63/E$43,"n/a")</f>
         <v/>
       </c>
-      <c r="F64" s="52">
+      <c r="F64" s="32">
         <f>IFERROR(F$63/F$43,"n/a")</f>
         <v/>
       </c>
-      <c r="G64" s="52">
+      <c r="G64" s="32">
         <f>IFERROR(G$63/G$43,"n/a")</f>
         <v/>
       </c>
-      <c r="H64" s="52">
+      <c r="H64" s="32">
         <f>IFERROR(H$63/H$43,"n/a")</f>
         <v/>
       </c>
-      <c r="I64" s="52">
+      <c r="I64" s="32">
         <f>IFERROR(I$63/I$43,"n/a")</f>
         <v/>
       </c>
@@ -13579,35 +13551,35 @@
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B65" s="52">
+      <c r="B65" s="32">
         <f>IFERROR(B$43/B$31,"n/a")</f>
         <v/>
       </c>
-      <c r="C65" s="52">
+      <c r="C65" s="32">
         <f>IFERROR(C$43/C$31,"n/a")</f>
         <v/>
       </c>
-      <c r="D65" s="52">
+      <c r="D65" s="32">
         <f>IFERROR(D$43/D$31,"n/a")</f>
         <v/>
       </c>
-      <c r="E65" s="52">
+      <c r="E65" s="32">
         <f>IFERROR(E$43/E$31,"n/a")</f>
         <v/>
       </c>
-      <c r="F65" s="52">
+      <c r="F65" s="32">
         <f>IFERROR(F$43/F$31,"n/a")</f>
         <v/>
       </c>
-      <c r="G65" s="52">
+      <c r="G65" s="32">
         <f>IFERROR(G$43/G$31,"n/a")</f>
         <v/>
       </c>
-      <c r="H65" s="52">
+      <c r="H65" s="32">
         <f>IFERROR(H$43/H$31,"n/a")</f>
         <v/>
       </c>
-      <c r="I65" s="52">
+      <c r="I65" s="32">
         <f>IFERROR(I$43/I$31,"n/a")</f>
         <v/>
       </c>
@@ -13633,35 +13605,35 @@
           <t>FCF</t>
         </is>
       </c>
-      <c r="B67" s="53">
+      <c r="B67" s="33">
         <f>IFERROR(B$55-ABS(B$54),"n/a")</f>
         <v/>
       </c>
-      <c r="C67" s="53">
+      <c r="C67" s="33">
         <f>IFERROR(C$55-ABS(C$54),"n/a")</f>
         <v/>
       </c>
-      <c r="D67" s="53">
+      <c r="D67" s="33">
         <f>IFERROR(D$55-ABS(D$54),"n/a")</f>
         <v/>
       </c>
-      <c r="E67" s="53">
+      <c r="E67" s="33">
         <f>IFERROR(E$55-ABS(E$54),"n/a")</f>
         <v/>
       </c>
-      <c r="F67" s="53">
+      <c r="F67" s="33">
         <f>IFERROR(F$55-ABS(F$54),"n/a")</f>
         <v/>
       </c>
-      <c r="G67" s="53">
+      <c r="G67" s="33">
         <f>IFERROR(G$55-ABS(G$54),"n/a")</f>
         <v/>
       </c>
-      <c r="H67" s="53">
+      <c r="H67" s="33">
         <f>IFERROR(H$55-ABS(H$54),"n/a")</f>
         <v/>
       </c>
-      <c r="I67" s="53">
+      <c r="I67" s="33">
         <f>IFERROR(I$55-ABS(I$54),"n/a")</f>
         <v/>
       </c>
@@ -13672,35 +13644,35 @@
           <t>FCF/DT</t>
         </is>
       </c>
-      <c r="B68" s="52">
+      <c r="B68" s="32">
         <f>IFERROR(B$67/B$43,"n/a")</f>
         <v/>
       </c>
-      <c r="C68" s="52">
+      <c r="C68" s="32">
         <f>IFERROR(C$67/C$43,"n/a")</f>
         <v/>
       </c>
-      <c r="D68" s="52">
+      <c r="D68" s="32">
         <f>IFERROR(D$67/D$43,"n/a")</f>
         <v/>
       </c>
-      <c r="E68" s="52">
+      <c r="E68" s="32">
         <f>IFERROR(E$67/E$43,"n/a")</f>
         <v/>
       </c>
-      <c r="F68" s="52">
+      <c r="F68" s="32">
         <f>IFERROR(F$67/F$43,"n/a")</f>
         <v/>
       </c>
-      <c r="G68" s="52">
+      <c r="G68" s="32">
         <f>IFERROR(G$67/G$43,"n/a")</f>
         <v/>
       </c>
-      <c r="H68" s="52">
+      <c r="H68" s="32">
         <f>IFERROR(H$67/H$43,"n/a")</f>
         <v/>
       </c>
-      <c r="I68" s="52">
+      <c r="I68" s="32">
         <f>IFERROR(I$67/I$43,"n/a")</f>
         <v/>
       </c>
@@ -13711,35 +13683,35 @@
           <t>FCF/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B69" s="52">
+      <c r="B69" s="32">
         <f>IFERROR(B$67/B$35,"n/a")</f>
         <v/>
       </c>
-      <c r="C69" s="52">
+      <c r="C69" s="32">
         <f>IFERROR(C$67/C$35,"n/a")</f>
         <v/>
       </c>
-      <c r="D69" s="52">
+      <c r="D69" s="32">
         <f>IFERROR(D$67/D$35,"n/a")</f>
         <v/>
       </c>
-      <c r="E69" s="52">
+      <c r="E69" s="32">
         <f>IFERROR(E$67/E$35,"n/a")</f>
         <v/>
       </c>
-      <c r="F69" s="52">
+      <c r="F69" s="32">
         <f>IFERROR(F$67/F$35,"n/a")</f>
         <v/>
       </c>
-      <c r="G69" s="52">
+      <c r="G69" s="32">
         <f>IFERROR(G$67/G$35,"n/a")</f>
         <v/>
       </c>
-      <c r="H69" s="52">
+      <c r="H69" s="32">
         <f>IFERROR(H$67/H$35,"n/a")</f>
         <v/>
       </c>
-      <c r="I69" s="52">
+      <c r="I69" s="32">
         <f>IFERROR(I$67/I$35,"n/a")</f>
         <v/>
       </c>
@@ -13750,35 +13722,35 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B70" s="53">
+      <c r="B70" s="33">
         <f>IFERROR(ABS(B$54),"n/a")</f>
         <v/>
       </c>
-      <c r="C70" s="53">
+      <c r="C70" s="33">
         <f>IFERROR(ABS(C$54),"n/a")</f>
         <v/>
       </c>
-      <c r="D70" s="53">
+      <c r="D70" s="33">
         <f>IFERROR(ABS(D$54),"n/a")</f>
         <v/>
       </c>
-      <c r="E70" s="53">
+      <c r="E70" s="33">
         <f>IFERROR(ABS(E$54),"n/a")</f>
         <v/>
       </c>
-      <c r="F70" s="53">
+      <c r="F70" s="33">
         <f>IFERROR(ABS(F$54),"n/a")</f>
         <v/>
       </c>
-      <c r="G70" s="53">
+      <c r="G70" s="33">
         <f>IFERROR(ABS(G$54),"n/a")</f>
         <v/>
       </c>
-      <c r="H70" s="53">
+      <c r="H70" s="33">
         <f>IFERROR(ABS(H$54),"n/a")</f>
         <v/>
       </c>
-      <c r="I70" s="53">
+      <c r="I70" s="33">
         <f>IFERROR(ABS(I$54),"n/a")</f>
         <v/>
       </c>
@@ -13789,35 +13761,35 @@
           <t>Capex/TS</t>
         </is>
       </c>
-      <c r="B71" s="52">
+      <c r="B71" s="32">
         <f>IFERROR(B$70/B$31,"n/a")</f>
         <v/>
       </c>
-      <c r="C71" s="52">
+      <c r="C71" s="32">
         <f>IFERROR(C$70/C$31,"n/a")</f>
         <v/>
       </c>
-      <c r="D71" s="52">
+      <c r="D71" s="32">
         <f>IFERROR(D$70/D$31,"n/a")</f>
         <v/>
       </c>
-      <c r="E71" s="52">
+      <c r="E71" s="32">
         <f>IFERROR(E$70/E$31,"n/a")</f>
         <v/>
       </c>
-      <c r="F71" s="52">
+      <c r="F71" s="32">
         <f>IFERROR(F$70/F$31,"n/a")</f>
         <v/>
       </c>
-      <c r="G71" s="52">
+      <c r="G71" s="32">
         <f>IFERROR(G$70/G$31,"n/a")</f>
         <v/>
       </c>
-      <c r="H71" s="52">
+      <c r="H71" s="32">
         <f>IFERROR(H$70/H$31,"n/a")</f>
         <v/>
       </c>
-      <c r="I71" s="52">
+      <c r="I71" s="32">
         <f>IFERROR(I$70/I$31,"n/a")</f>
         <v/>
       </c>
@@ -13828,35 +13800,35 @@
           <t>Capex/LNST</t>
         </is>
       </c>
-      <c r="B72" s="52">
+      <c r="B72" s="32">
         <f>IFERROR(B$70/ABS(B$50),"n/a")</f>
         <v/>
       </c>
-      <c r="C72" s="52">
+      <c r="C72" s="32">
         <f>IFERROR(C$70/ABS(C$50),"n/a")</f>
         <v/>
       </c>
-      <c r="D72" s="52">
+      <c r="D72" s="32">
         <f>IFERROR(D$70/ABS(D$50),"n/a")</f>
         <v/>
       </c>
-      <c r="E72" s="52">
+      <c r="E72" s="32">
         <f>IFERROR(E$70/ABS(E$50),"n/a")</f>
         <v/>
       </c>
-      <c r="F72" s="52">
+      <c r="F72" s="32">
         <f>IFERROR(F$70/ABS(F$50),"n/a")</f>
         <v/>
       </c>
-      <c r="G72" s="52">
+      <c r="G72" s="32">
         <f>IFERROR(G$70/ABS(G$50),"n/a")</f>
         <v/>
       </c>
-      <c r="H72" s="52">
+      <c r="H72" s="32">
         <f>IFERROR(H$70/ABS(H$50),"n/a")</f>
         <v/>
       </c>
-      <c r="I72" s="52">
+      <c r="I72" s="32">
         <f>IFERROR(I$70/ABS(I$50),"n/a")</f>
         <v/>
       </c>
@@ -13867,35 +13839,35 @@
           <t>Chi phí khấu hao/Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B73" s="52">
+      <c r="B73" s="32">
         <f>IFERROR(ABS(B$53)/B$45,"n/a")</f>
         <v/>
       </c>
-      <c r="C73" s="52">
+      <c r="C73" s="32">
         <f>IFERROR(ABS(C$53)/C$45,"n/a")</f>
         <v/>
       </c>
-      <c r="D73" s="52">
+      <c r="D73" s="32">
         <f>IFERROR(ABS(D$53)/D$45,"n/a")</f>
         <v/>
       </c>
-      <c r="E73" s="52">
+      <c r="E73" s="32">
         <f>IFERROR(ABS(E$53)/E$45,"n/a")</f>
         <v/>
       </c>
-      <c r="F73" s="52">
+      <c r="F73" s="32">
         <f>IFERROR(ABS(F$53)/F$45,"n/a")</f>
         <v/>
       </c>
-      <c r="G73" s="52">
+      <c r="G73" s="32">
         <f>IFERROR(ABS(G$53)/G$45,"n/a")</f>
         <v/>
       </c>
-      <c r="H73" s="52">
+      <c r="H73" s="32">
         <f>IFERROR(ABS(H$53)/H$45,"n/a")</f>
         <v/>
       </c>
-      <c r="I73" s="52">
+      <c r="I73" s="32">
         <f>IFERROR(ABS(I$53)/I$45,"n/a")</f>
         <v/>
       </c>
@@ -13906,35 +13878,35 @@
           <t>EBIT/Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B74" s="54">
+      <c r="B74" s="34">
         <f>IFERROR(B$63/ABS(B$49),"n/a")</f>
         <v/>
       </c>
-      <c r="C74" s="54">
+      <c r="C74" s="34">
         <f>IFERROR(C$63/ABS(C$49),"n/a")</f>
         <v/>
       </c>
-      <c r="D74" s="54">
+      <c r="D74" s="34">
         <f>IFERROR(D$63/ABS(D$49),"n/a")</f>
         <v/>
       </c>
-      <c r="E74" s="54">
+      <c r="E74" s="34">
         <f>IFERROR(E$63/ABS(E$49),"n/a")</f>
         <v/>
       </c>
-      <c r="F74" s="54">
+      <c r="F74" s="34">
         <f>IFERROR(F$63/ABS(F$49),"n/a")</f>
         <v/>
       </c>
-      <c r="G74" s="54">
+      <c r="G74" s="34">
         <f>IFERROR(G$63/ABS(G$49),"n/a")</f>
         <v/>
       </c>
-      <c r="H74" s="54">
+      <c r="H74" s="34">
         <f>IFERROR(H$63/ABS(H$49),"n/a")</f>
         <v/>
       </c>
-      <c r="I74" s="54">
+      <c r="I74" s="34">
         <f>IFERROR(I$63/ABS(I$49),"n/a")</f>
         <v/>
       </c>
@@ -13999,35 +13971,35 @@
           <t>HTK/DT</t>
         </is>
       </c>
-      <c r="B77" s="52">
+      <c r="B77" s="32">
         <f>IFERROR(B$28/B$43,"n/a")</f>
         <v/>
       </c>
-      <c r="C77" s="52">
+      <c r="C77" s="32">
         <f>IFERROR(C$28/C$43,"n/a")</f>
         <v/>
       </c>
-      <c r="D77" s="52">
+      <c r="D77" s="32">
         <f>IFERROR(D$28/D$43,"n/a")</f>
         <v/>
       </c>
-      <c r="E77" s="52">
+      <c r="E77" s="32">
         <f>IFERROR(E$28/E$43,"n/a")</f>
         <v/>
       </c>
-      <c r="F77" s="52">
+      <c r="F77" s="32">
         <f>IFERROR(F$28/F$43,"n/a")</f>
         <v/>
       </c>
-      <c r="G77" s="52">
+      <c r="G77" s="32">
         <f>IFERROR(G$28/G$43,"n/a")</f>
         <v/>
       </c>
-      <c r="H77" s="52">
+      <c r="H77" s="32">
         <f>IFERROR(H$28/H$43,"n/a")</f>
         <v/>
       </c>
-      <c r="I77" s="52">
+      <c r="I77" s="32">
         <f>IFERROR(I$28/I$43,"n/a")</f>
         <v/>
       </c>
@@ -14038,35 +14010,35 @@
           <t>HTK/TS</t>
         </is>
       </c>
-      <c r="B78" s="52">
+      <c r="B78" s="32">
         <f>IFERROR(B$28/B$31,"n/a")</f>
         <v/>
       </c>
-      <c r="C78" s="52">
+      <c r="C78" s="32">
         <f>IFERROR(C$28/C$31,"n/a")</f>
         <v/>
       </c>
-      <c r="D78" s="52">
+      <c r="D78" s="32">
         <f>IFERROR(D$28/D$31,"n/a")</f>
         <v/>
       </c>
-      <c r="E78" s="52">
+      <c r="E78" s="32">
         <f>IFERROR(E$28/E$31,"n/a")</f>
         <v/>
       </c>
-      <c r="F78" s="52">
+      <c r="F78" s="32">
         <f>IFERROR(F$28/F$31,"n/a")</f>
         <v/>
       </c>
-      <c r="G78" s="52">
+      <c r="G78" s="32">
         <f>IFERROR(G$28/G$31,"n/a")</f>
         <v/>
       </c>
-      <c r="H78" s="52">
+      <c r="H78" s="32">
         <f>IFERROR(H$28/H$31,"n/a")</f>
         <v/>
       </c>
-      <c r="I78" s="52">
+      <c r="I78" s="32">
         <f>IFERROR(I$28/I$31,"n/a")</f>
         <v/>
       </c>
@@ -14077,35 +14049,35 @@
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B79" s="52">
+      <c r="B79" s="32">
         <f>IFERROR(B$43/B$31,"n/a")</f>
         <v/>
       </c>
-      <c r="C79" s="52">
+      <c r="C79" s="32">
         <f>IFERROR(C$43/C$31,"n/a")</f>
         <v/>
       </c>
-      <c r="D79" s="52">
+      <c r="D79" s="32">
         <f>IFERROR(D$43/D$31,"n/a")</f>
         <v/>
       </c>
-      <c r="E79" s="52">
+      <c r="E79" s="32">
         <f>IFERROR(E$43/E$31,"n/a")</f>
         <v/>
       </c>
-      <c r="F79" s="52">
+      <c r="F79" s="32">
         <f>IFERROR(F$43/F$31,"n/a")</f>
         <v/>
       </c>
-      <c r="G79" s="52">
+      <c r="G79" s="32">
         <f>IFERROR(G$43/G$31,"n/a")</f>
         <v/>
       </c>
-      <c r="H79" s="52">
+      <c r="H79" s="32">
         <f>IFERROR(H$43/H$31,"n/a")</f>
         <v/>
       </c>
-      <c r="I79" s="52">
+      <c r="I79" s="32">
         <f>IFERROR(I$43/I$31,"n/a")</f>
         <v/>
       </c>
@@ -14131,35 +14103,35 @@
           <t>(TS ngắn hạn − HTK)/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B81" s="54">
+      <c r="B81" s="34">
         <f>IFERROR((B$29-B$28)/B$35,"n/a")</f>
         <v/>
       </c>
-      <c r="C81" s="54">
+      <c r="C81" s="34">
         <f>IFERROR((C$29-C$28)/C$35,"n/a")</f>
         <v/>
       </c>
-      <c r="D81" s="54">
+      <c r="D81" s="34">
         <f>IFERROR((D$29-D$28)/D$35,"n/a")</f>
         <v/>
       </c>
-      <c r="E81" s="54">
+      <c r="E81" s="34">
         <f>IFERROR((E$29-E$28)/E$35,"n/a")</f>
         <v/>
       </c>
-      <c r="F81" s="54">
+      <c r="F81" s="34">
         <f>IFERROR((F$29-F$28)/F$35,"n/a")</f>
         <v/>
       </c>
-      <c r="G81" s="54">
+      <c r="G81" s="34">
         <f>IFERROR((G$29-G$28)/G$35,"n/a")</f>
         <v/>
       </c>
-      <c r="H81" s="54">
+      <c r="H81" s="34">
         <f>IFERROR((H$29-H$28)/H$35,"n/a")</f>
         <v/>
       </c>
-      <c r="I81" s="54">
+      <c r="I81" s="34">
         <f>IFERROR((I$29-I$28)/I$35,"n/a")</f>
         <v/>
       </c>
@@ -14170,35 +14142,35 @@
           <t>TS ngắn hạn/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B82" s="54">
+      <c r="B82" s="34">
         <f>IFERROR(B$29/B$35,"n/a")</f>
         <v/>
       </c>
-      <c r="C82" s="54">
+      <c r="C82" s="34">
         <f>IFERROR(C$29/C$35,"n/a")</f>
         <v/>
       </c>
-      <c r="D82" s="54">
+      <c r="D82" s="34">
         <f>IFERROR(D$29/D$35,"n/a")</f>
         <v/>
       </c>
-      <c r="E82" s="54">
+      <c r="E82" s="34">
         <f>IFERROR(E$29/E$35,"n/a")</f>
         <v/>
       </c>
-      <c r="F82" s="54">
+      <c r="F82" s="34">
         <f>IFERROR(F$29/F$35,"n/a")</f>
         <v/>
       </c>
-      <c r="G82" s="54">
+      <c r="G82" s="34">
         <f>IFERROR(G$29/G$35,"n/a")</f>
         <v/>
       </c>
-      <c r="H82" s="54">
+      <c r="H82" s="34">
         <f>IFERROR(H$29/H$35,"n/a")</f>
         <v/>
       </c>
-      <c r="I82" s="54">
+      <c r="I82" s="34">
         <f>IFERROR(I$29/I$35,"n/a")</f>
         <v/>
       </c>
@@ -14224,35 +14196,35 @@
           <t>TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B84" s="53">
+      <c r="B84" s="33">
         <f>IFERROR(B$30,"n/a")</f>
         <v/>
       </c>
-      <c r="C84" s="53">
+      <c r="C84" s="33">
         <f>IFERROR(C$30,"n/a")</f>
         <v/>
       </c>
-      <c r="D84" s="53">
+      <c r="D84" s="33">
         <f>IFERROR(D$30,"n/a")</f>
         <v/>
       </c>
-      <c r="E84" s="53">
+      <c r="E84" s="33">
         <f>IFERROR(E$30,"n/a")</f>
         <v/>
       </c>
-      <c r="F84" s="53">
+      <c r="F84" s="33">
         <f>IFERROR(F$30,"n/a")</f>
         <v/>
       </c>
-      <c r="G84" s="53">
+      <c r="G84" s="33">
         <f>IFERROR(G$30,"n/a")</f>
         <v/>
       </c>
-      <c r="H84" s="53">
+      <c r="H84" s="33">
         <f>IFERROR(H$30,"n/a")</f>
         <v/>
       </c>
-      <c r="I84" s="53">
+      <c r="I84" s="33">
         <f>IFERROR(I$30,"n/a")</f>
         <v/>
       </c>
@@ -14263,48 +14235,40 @@
           <t>Tài sản vô hình/Giá trị sổ sách</t>
         </is>
       </c>
-      <c r="B85" s="52">
+      <c r="B85" s="32">
         <f>IFERROR(B$30/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C85" s="52">
+      <c r="C85" s="32">
         <f>IFERROR(C$30/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D85" s="52">
+      <c r="D85" s="32">
         <f>IFERROR(D$30/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E85" s="52">
+      <c r="E85" s="32">
         <f>IFERROR(E$30/E$39,"n/a")</f>
         <v/>
       </c>
-      <c r="F85" s="52">
+      <c r="F85" s="32">
         <f>IFERROR(F$30/F$39,"n/a")</f>
         <v/>
       </c>
-      <c r="G85" s="52">
+      <c r="G85" s="32">
         <f>IFERROR(G$30/G$39,"n/a")</f>
         <v/>
       </c>
-      <c r="H85" s="52">
+      <c r="H85" s="32">
         <f>IFERROR(H$30/H$39,"n/a")</f>
         <v/>
       </c>
-      <c r="I85" s="52">
+      <c r="I85" s="32">
         <f>IFERROR(I$30/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:J2">
-    <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="3">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B6:I6">
     <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.3</formula>
@@ -14340,6 +14304,14 @@
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B2:J2">
+    <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="3">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B4:J5">
     <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="3">
       <formula>0.1</formula>
@@ -14368,13 +14340,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="7.6640625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
+    <col width="7.625" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
     <col width="20" bestFit="1" customWidth="1" style="5" min="2" max="5"/>
-    <col width="17.44140625" customWidth="1" style="5" min="6" max="7"/>
-    <col width="7.6640625" customWidth="1" style="5" min="8" max="18"/>
-    <col width="12.6640625" customWidth="1" style="5" min="19" max="16384"/>
+    <col width="17.5" customWidth="1" style="5" min="6" max="7"/>
+    <col width="7.625" customWidth="1" style="5" min="8" max="18"/>
+    <col width="12.625" customWidth="1" style="5" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -14406,16 +14378,16 @@
           <t>Số CP</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="46" t="n">
         <v>1475765646</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="46" t="n">
         <v>1475765646</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="46" t="n">
         <v>1475765646</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="46" t="n">
         <v>1475765646</v>
       </c>
     </row>
@@ -14425,21 +14397,17 @@
           <t>Thị giá</t>
         </is>
       </c>
-      <c r="B3" s="6">
-        <f>[1]Sheet1!$G$2</f>
-        <v/>
-      </c>
-      <c r="C3" s="6">
-        <f>[1]Sheet1!$G$2</f>
-        <v/>
-      </c>
-      <c r="D3" s="6">
-        <f>[1]Sheet1!$G$2</f>
-        <v/>
-      </c>
-      <c r="E3" s="6">
-        <f>[1]Sheet1!$G$2</f>
-        <v/>
+      <c r="B3" s="46" t="n">
+        <v>75100</v>
+      </c>
+      <c r="C3" s="46" t="n">
+        <v>75100</v>
+      </c>
+      <c r="D3" s="46" t="n">
+        <v>75100</v>
+      </c>
+      <c r="E3" s="46" t="n">
+        <v>75100</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -14448,19 +14416,19 @@
           <t>Vốn hoá</t>
         </is>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="46">
         <f>B2*B3</f>
         <v/>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="46">
         <f>C2*C3</f>
         <v/>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="46">
         <f>D2*D3</f>
         <v/>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="46">
         <f>E2*E3</f>
         <v/>
       </c>
@@ -14472,22 +14440,22 @@
           <t>VCSH</t>
         </is>
       </c>
-      <c r="B6" s="55" t="n">
+      <c r="B6" s="47" t="n">
         <v>35933000000000</v>
       </c>
-      <c r="C6" s="55" t="n">
+      <c r="C6" s="47" t="n">
         <v>36351000000000</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="47">
         <f>B6*(($E$6/B6)^(2/3))</f>
         <v/>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="46">
         <f>chi_so_tai_chinh!J39</f>
         <v/>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
+      <c r="F6" s="48" t="n"/>
+      <c r="G6" s="48" t="n"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -14495,17 +14463,17 @@
           <t>LICĐTS</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="46" t="n">
         <v>619000000000</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="46" t="n">
         <v>672000000000</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="46">
         <f>D6*0.02</f>
         <v/>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="46">
         <f>E6*0.02</f>
         <v/>
       </c>
@@ -14518,19 +14486,19 @@
           <t>BV</t>
         </is>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="46">
         <f>B6-B7</f>
         <v/>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="46">
         <f>C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="46">
         <f>D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="46">
         <f>E6-E7</f>
         <v/>
       </c>
@@ -14541,19 +14509,19 @@
           <t>BVPS</t>
         </is>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="49">
         <f>B8/B2</f>
         <v/>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="49">
         <f>C8/C2</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="49">
         <f>D8/D2</f>
         <v/>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="49">
         <f>E8/E2</f>
         <v/>
       </c>
@@ -14564,19 +14532,19 @@
           <t>PB</t>
         </is>
       </c>
-      <c r="B10" s="56">
+      <c r="B10" s="50">
         <f>B3/B9</f>
         <v/>
       </c>
-      <c r="C10" s="56">
+      <c r="C10" s="50">
         <f>C3/C9</f>
         <v/>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="50">
         <f>D3/D9</f>
         <v/>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="50">
         <f>E3/E9</f>
         <v/>
       </c>
